--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N115_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N115_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.48901343308969</v>
+        <v>7.391964682877075</v>
       </c>
       <c r="D2" t="n">
-        <v>17.66714224066781</v>
+        <v>2.87091061410852</v>
       </c>
       <c r="E2" t="n">
-        <v>17.55738661296422</v>
+        <v>2.853075324606686</v>
       </c>
       <c r="F2" t="n">
-        <v>21.62752207872992</v>
+        <v>3.514472337793612</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.07865482917201</v>
+        <v>10.90028140974045</v>
       </c>
       <c r="D3" t="n">
-        <v>66.85310708781083</v>
+        <v>10.86362990176926</v>
       </c>
       <c r="E3" t="n">
-        <v>17.55738661296422</v>
+        <v>2.853075324606686</v>
       </c>
       <c r="F3" t="n">
-        <v>21.62752207872992</v>
+        <v>3.514472337793612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.02636051574538</v>
+        <v>10.89178358380862</v>
       </c>
       <c r="D4" t="n">
-        <v>66.70263458256021</v>
+        <v>10.83917811966603</v>
       </c>
       <c r="E4" t="n">
-        <v>17.55738661296422</v>
+        <v>2.853075324606686</v>
       </c>
       <c r="F4" t="n">
-        <v>21.62752207872992</v>
+        <v>3.514472337793612</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.97414629837028</v>
+        <v>3.895798773485171</v>
       </c>
       <c r="D5" t="n">
-        <v>24.10535310075388</v>
+        <v>3.917119878872506</v>
       </c>
       <c r="E5" t="n">
-        <v>17.55738661296422</v>
+        <v>2.853075324606686</v>
       </c>
       <c r="F5" t="n">
-        <v>21.62752207872992</v>
+        <v>3.514472337793612</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.49380167624823</v>
+        <v>5.442742772390338</v>
       </c>
       <c r="D6" t="n">
-        <v>31.96914745320096</v>
+        <v>5.194986461145156</v>
       </c>
       <c r="E6" t="n">
-        <v>17.55738661296422</v>
+        <v>2.853075324606686</v>
       </c>
       <c r="F6" t="n">
-        <v>21.62752207872992</v>
+        <v>3.514472337793612</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.35200588366801</v>
+        <v>10.94470095609605</v>
       </c>
       <c r="D7" t="n">
-        <v>67.54712107879222</v>
+        <v>10.97640717530374</v>
       </c>
       <c r="E7" t="n">
-        <v>17.55738661296422</v>
+        <v>2.853075324606686</v>
       </c>
       <c r="F7" t="n">
-        <v>21.62752207872992</v>
+        <v>3.514472337793612</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
